--- a/naver-place-crawler/results_health/고양_헬스장.xlsx
+++ b/naver-place-crawler/results_health/고양_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="49" customWidth="1" min="7" max="7"/>
-    <col width="49" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>휘트니스칸 백석점 헬스&amp;PT&amp;요가&amp;필라테스</t>
+          <t>스포애니 화정역점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>kann666@naver.com</t>
+          <t>spoany102@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1428-1174</t>
+          <t>0507-1380-9618</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1080 남정골드프라자 9층</t>
+          <t>경기 고양시 덕양구 화신로260번길 57 지하1층 11호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fktp</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1176</v>
+        <v>1446</v>
       </c>
       <c r="Q2" t="n">
-        <v>874</v>
+        <v>1942</v>
       </c>
       <c r="R2" t="n">
-        <v>2050</v>
+        <v>3388</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,24 +640,24 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1533278650</t>
+          <t>1849085200</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533278650</t>
+          <t>https://m.place.naver.com/place/1849085200</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -675,12 +679,12 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 백양로 65 201호</t>
+          <t>경기 고양시 덕양구 백양로 65 201호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/movegym24</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +694,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsgemoy</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2278</v>
+        <v>2312</v>
       </c>
       <c r="Q3" t="n">
-        <v>718</v>
+        <v>741</v>
       </c>
       <c r="R3" t="n">
-        <v>2996</v>
+        <v>3053</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,41 +748,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>휘트니스칸 헬스&amp;PT&amp;요가&amp;필라테스 주엽점</t>
+          <t>인프라짐 PT 대화역헬스장</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>kann5555@naver.com</t>
+          <t>infragym1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1396-3191</t>
+          <t>0507-1331-5665</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1388 태영프라자 서관 3층</t>
+          <t>경기 고양시 일산서구 중앙로 1574 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://fitnesskann.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -794,13 +802,17 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5u9v3</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2037</v>
+        <v>2433</v>
       </c>
       <c r="Q4" t="n">
-        <v>885</v>
+        <v>2030</v>
       </c>
       <c r="R4" t="n">
-        <v>2922</v>
+        <v>4463</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1797149054</t>
+          <t>11579499</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1797149054</t>
+          <t>https://m.place.naver.com/place/11579499</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>인프라짐 PT 대화역헬스장</t>
+          <t>5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>infragym1@naver.com</t>
+          <t>5150fitness2@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1331-5665</t>
+          <t>0507-1348-8027</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1574 8층</t>
+          <t>경기 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/infragym1</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,23 +890,27 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vwhp</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2376</v>
+        <v>1221</v>
       </c>
       <c r="Q5" t="n">
-        <v>2022</v>
+        <v>1612</v>
       </c>
       <c r="R5" t="n">
-        <v>4398</v>
+        <v>2833</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +934,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11579499</t>
+          <t>1817673935</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11579499</t>
+          <t>https://m.place.naver.com/place/1817673935</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>핏포유 탄현점 헬스PT</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fit4u2019@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1363-6711</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 산현로 7 풍성프라자 9층 핏포유</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fit4u2019</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -972,20 +988,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42s1j</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>526</v>
+        <v>304</v>
       </c>
       <c r="Q6" t="n">
-        <v>4952</v>
+        <v>268</v>
       </c>
       <c r="R6" t="n">
-        <v>5478</v>
+        <v>572</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,74 +1032,78 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>60823193</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/60823193</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>디벨롭피트니스 본점헬스&amp;PT&amp;GX&amp;골프&amp;스쿼시&amp;필라테스</t>
+          <t>액트짐 일산역점 헬스&amp;GX&amp;PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>developfitness@naver.com</t>
+          <t>actgym_02@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1374-2418</t>
+          <t>0507-1445-5805</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 중앙로 1406 한솔코아 7층</t>
+          <t>경기 고양시 일산서구 원일로 69 6층 601호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/developfitness</t>
+          <t>https://booking.naver.com/booking/6/bizes/1386810</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wu9oxes</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>703</v>
+        <v>240</v>
       </c>
       <c r="Q7" t="n">
-        <v>1004</v>
+        <v>438</v>
       </c>
       <c r="R7" t="n">
-        <v>1707</v>
+        <v>678</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,61 +1130,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1332252606</t>
+          <t>1033726767</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1332252606</t>
+          <t>https://m.place.naver.com/place/1033726767</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>베르만짐 헬스&amp;PT 식사점</t>
+          <t>레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>qpfmaks02@naver.com</t>
+          <t>readybody2@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1349-2708</t>
+          <t>0507-1359-9680</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 위시티로 24 3층</t>
+          <t>경기 고양시 일산서구 일현로 47 예일큰프라자 6층 레디바디 탄현점 헬스PT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_xhhtNn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,13 +1194,17 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w461vb</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>324</v>
+        <v>671</v>
       </c>
       <c r="Q8" t="n">
-        <v>679</v>
+        <v>1047</v>
       </c>
       <c r="R8" t="n">
-        <v>1003</v>
+        <v>1718</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1722963960</t>
+          <t>776760797</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1722963960</t>
+          <t>https://m.place.naver.com/place/776760797</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>리조트휘트니스 헬스&amp;PT 롯데백화점 일산점</t>
+          <t>세븐짐 탄현점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>resort_13@naver.com</t>
+          <t>sevengym1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1434-4080</t>
+          <t>0507-1488-5258</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산동구 중앙로 1283 10층</t>
+          <t>경기 고양시 일산서구 산현로17번길 9 부건3차프라자 6층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/resort_13</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,20 +1282,24 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5uzxl</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>558</v>
+        <v>168</v>
       </c>
       <c r="Q9" t="n">
-        <v>895</v>
+        <v>152</v>
       </c>
       <c r="R9" t="n">
-        <v>1453</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1379874016</t>
+          <t>12753889</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1379874016</t>
+          <t>https://m.place.naver.com/place/12753889</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1986피트니스 헬스PT 지축점</t>
+          <t>버클다운짐 탄현점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1986fitness6@naver.com</t>
+          <t>buckledown1234@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1304-2474</t>
+          <t>0507-1358-3972</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 고양시 덕양구 지축로 70 푸리마타워 9층 1986피트니스</t>
+          <t>경기 고양시 일산서구 일현로 107 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/1986fitness6</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1348,20 +1380,24 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tj13</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1019</v>
+        <v>1242</v>
       </c>
       <c r="Q10" t="n">
-        <v>993</v>
+        <v>1085</v>
       </c>
       <c r="R10" t="n">
-        <v>2012</v>
+        <v>2327</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1814490801</t>
+          <t>1918164834</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1814490801</t>
+          <t>https://m.place.naver.com/place/1918164834</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,39 +1446,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>짐케어 일산 탄현점 헬스&amp;PT</t>
+          <t>바디오프짐 PT&amp;필라테스 일산장항점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gymcare24@naver.com</t>
+          <t>bodyoffgym@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1483-3436</t>
+          <t>0507-1381-8260</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 고양시 일산서구 일현로 67 까뮤이스테이트 2층 201~205호</t>
+          <t>경기 고양시 일산동구 무궁화로 20-38 로데오탑 211호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_elwnn</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1458,7 +1494,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>681</v>
+        <v>133</v>
       </c>
       <c r="Q11" t="n">
-        <v>1550</v>
+        <v>510</v>
       </c>
       <c r="R11" t="n">
-        <v>2231</v>
+        <v>643</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,957 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1924109138</t>
+          <t>32507674</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1924109138</t>
+          <t>https://m.place.naver.com/place/32507674</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>고포잇짐 헬스&amp;PT 장항점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>go4itgym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1315-5550</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 백마로 195 SK엠시티타워 2층 2110,2111호</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/go4itgym1</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>163</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>777</v>
-      </c>
-      <c r="R12" t="n">
-        <v>940</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1738952122</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1738952122</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>헬스보이짐 골프인 필라걸 일산 주엽점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>healthboy67@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1373-7656</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 중앙로 1496 1층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://linktr.ee/healthboygym67</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>611</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>792</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1403</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1251452457</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1251452457</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>버클다운짐 탄현점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>buckledown1234@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1358-3972</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일현로 107 4층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/buckledowngym.kr</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1228</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1082</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2310</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1918164834</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1918164834</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>투게더휘트니스 일산점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>togetherfitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1461-1485</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일산로 562 신일산연합상가 B1 투게더트니스</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/togetherfitness</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1321</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>293</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1614</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1161506645</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1161506645</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>스포애니 화정역점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>spoany102@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1380-9618</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 고양시 덕양구 화신로260번길 57 지하1층 11호</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/spoany_102</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1428</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1909</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3337</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1849085200</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1849085200</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5150피트니스 일산 대화점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5150fitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1348-8027</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 중앙로 1564 그린월드빌딩 6층 5150피트니스 일산 대화점</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/5150fitness2</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>1208</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1612</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2820</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1817673935</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1817673935</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>스포애니 마두역점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>spoany64@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1369-7697</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 중앙로 1190 서울타워 지하1층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/spoany64</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>489</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2184</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2673</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1639489562</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1639489562</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>리지트 피트니스 삼송점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>legitfitness02@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1398-8961</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 고양시 덕양구 동세로 63 2층 202호,203호,203-1호</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/legitfitness02</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>285</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>120</v>
-      </c>
-      <c r="R19" t="n">
-        <v>405</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1015991314</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1015991314</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>짐박스피트니스 탄현제니스점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>gymboxx@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>info@suppliesfitness.com</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1458-0638</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산서구 일현로 97-11 일산두산위브더제니스 B2층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://gymboxx.com/onceinayear?gym=80</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>740</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>33</v>
-      </c>
-      <c r="R20" t="n">
-        <v>773</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>2038926940</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2038926940</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>식스틴 휘트니스</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>sixteen_fitness@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 고양시 일산동구 성석로 7 2층</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/s1xteen_fitness_golf/</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>173</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>430</v>
-      </c>
-      <c r="R21" t="n">
-        <v>603</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1004973811</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1004973811</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
